--- a/output/roomself_excel/6363.xlsx
+++ b/output/roomself_excel/6363.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>350571</v>
+        <v>90172</v>
       </c>
       <c r="D2" t="n">
-        <v>6496</v>
+        <v>2544</v>
       </c>
       <c r="E2" t="n">
-        <v>1208</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105060</v>
+        <v>89958</v>
       </c>
       <c r="D3" t="n">
-        <v>2596</v>
+        <v>2536</v>
       </c>
       <c r="E3" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105400</v>
+        <v>211864</v>
       </c>
       <c r="D4" t="n">
-        <v>2600</v>
+        <v>3764</v>
       </c>
       <c r="E4" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>351552</v>
+        <v>213192</v>
       </c>
       <c r="D5" t="n">
-        <v>6528</v>
+        <v>3772</v>
       </c>
       <c r="E5" t="n">
-        <v>1208</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76944</v>
+        <v>105060</v>
       </c>
       <c r="D6" t="n">
-        <v>2504</v>
+        <v>2596</v>
       </c>
       <c r="E6" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>77280</v>
+        <v>105400</v>
       </c>
       <c r="D7" t="n">
-        <v>2512</v>
+        <v>2600</v>
       </c>
       <c r="E7" t="n">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34128</v>
+        <v>75885</v>
       </c>
       <c r="D8" t="n">
-        <v>1496</v>
+        <v>2440</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -620,14 +620,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22400</v>
+        <v>75736</v>
       </c>
       <c r="D9" t="n">
-        <v>1200</v>
+        <v>2444</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -642,14 +642,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22560</v>
+        <v>76454</v>
       </c>
       <c r="D10" t="n">
-        <v>1204</v>
+        <v>2220</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -664,14 +664,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34128</v>
+        <v>74750</v>
       </c>
       <c r="D11" t="n">
-        <v>1496</v>
+        <v>2196</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -686,14 +686,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>245926</v>
+        <v>34128</v>
       </c>
       <c r="D12" t="n">
-        <v>4004</v>
+        <v>1496</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -708,14 +708,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>245080</v>
+        <v>34128</v>
       </c>
       <c r="D13" t="n">
-        <v>3762</v>
+        <v>1496</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -730,14 +730,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67030</v>
+        <v>22862</v>
       </c>
       <c r="D14" t="n">
-        <v>2452</v>
+        <v>1212</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -752,14 +752,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67448</v>
+        <v>22701</v>
       </c>
       <c r="D15" t="n">
-        <v>2456</v>
+        <v>1208</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -774,14 +774,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22862</v>
+        <v>48188</v>
       </c>
       <c r="D16" t="n">
-        <v>1212</v>
+        <v>2148</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -796,14 +796,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22701</v>
+        <v>48749</v>
       </c>
       <c r="D17" t="n">
-        <v>1208</v>
+        <v>2136</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>75885</v>
+        <v>76944</v>
       </c>
       <c r="D18" t="n">
-        <v>2440</v>
+        <v>2504</v>
       </c>
       <c r="E18" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>75736</v>
+        <v>77280</v>
       </c>
       <c r="D19" t="n">
-        <v>2444</v>
+        <v>2512</v>
       </c>
       <c r="E19" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>76454</v>
+        <v>245926</v>
       </c>
       <c r="D20" t="n">
-        <v>2220</v>
+        <v>4004</v>
       </c>
       <c r="E20" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>74750</v>
+        <v>245080</v>
       </c>
       <c r="D21" t="n">
-        <v>2196</v>
+        <v>3762</v>
       </c>
       <c r="E21" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>805</v>
+        <v>22400</v>
       </c>
       <c r="D22" t="n">
-        <v>232</v>
+        <v>1200</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -932,15 +932,103 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>22560</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>67030</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2452</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>67448</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2456</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>805</v>
+      </c>
+      <c r="D26" t="n">
+        <v>232</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>875</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D27" t="n">
         <v>240</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/roomself_excel/6363.xlsx
+++ b/output/roomself_excel/6363.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>Perimeter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallLength</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallWidth</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -475,12 +465,6 @@
       <c r="D2" t="n">
         <v>2544</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +481,6 @@
       <c r="D3" t="n">
         <v>2536</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +497,6 @@
       <c r="D4" t="n">
         <v>3764</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +513,6 @@
       <c r="D5" t="n">
         <v>3772</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +529,6 @@
       <c r="D6" t="n">
         <v>2596</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +545,6 @@
       <c r="D7" t="n">
         <v>2600</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +561,6 @@
       <c r="D8" t="n">
         <v>2440</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +577,6 @@
       <c r="D9" t="n">
         <v>2444</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +593,6 @@
       <c r="D10" t="n">
         <v>2220</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +609,6 @@
       <c r="D11" t="n">
         <v>2196</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +625,6 @@
       <c r="D12" t="n">
         <v>1496</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +641,6 @@
       <c r="D13" t="n">
         <v>1496</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +657,6 @@
       <c r="D14" t="n">
         <v>1212</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +673,6 @@
       <c r="D15" t="n">
         <v>1208</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +689,6 @@
       <c r="D16" t="n">
         <v>2148</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +705,6 @@
       <c r="D17" t="n">
         <v>2136</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +721,6 @@
       <c r="D18" t="n">
         <v>2504</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +737,6 @@
       <c r="D19" t="n">
         <v>2512</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +753,6 @@
       <c r="D20" t="n">
         <v>4004</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +769,6 @@
       <c r="D21" t="n">
         <v>3762</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +785,6 @@
       <c r="D22" t="n">
         <v>1200</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +801,6 @@
       <c r="D23" t="n">
         <v>1204</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +817,6 @@
       <c r="D24" t="n">
         <v>2452</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +833,6 @@
       <c r="D25" t="n">
         <v>2456</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +849,6 @@
       <c r="D26" t="n">
         <v>232</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1024,12 +864,6 @@
       </c>
       <c r="D27" t="n">
         <v>240</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/6363.xlsx
+++ b/output/roomself_excel/6363.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
